--- a/CodeSystem-pcor-score-catalogue.xlsx
+++ b/CodeSystem-pcor-score-catalogue.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:40:42+00:00</t>
+    <t>2026-09-30T19:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-pcor-score-catalogue.xlsx
+++ b/CodeSystem-pcor-score-catalogue.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:42:59+00:00</t>
+    <t>2026-09-30T19:54:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-pcor-score-catalogue.xlsx
+++ b/CodeSystem-pcor-score-catalogue.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:54:40+00:00</t>
+    <t>2026-10-01T09:59:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>1</t>
   </si>
   <si>
     <t>Level</t>
@@ -135,25 +135,10 @@
     <t>Definition</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>promis-propr-utility</t>
   </si>
   <si>
     <t>PROMIS-Preference (PROPr) Utility Score</t>
-  </si>
-  <si>
-    <t>erq-s-reappraisal</t>
-  </si>
-  <si>
-    <t>ERQ-S Cognitive Reappraisal Subscale Score (3-21)</t>
-  </si>
-  <si>
-    <t>erq-s-suppression</t>
-  </si>
-  <si>
-    <t>ERQ-S Expressive Suppression Subscale Score (3-21)</t>
   </si>
 </sst>
 </file>
@@ -463,7 +448,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -482,39 +467,15 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>40</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="C2" t="s" s="2">
         <v>41</v>
       </c>
-      <c r="C2" t="s" s="2">
-        <v>42</v>
-      </c>
       <c r="D2" s="2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="D4" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/CodeSystem-pcor-score-catalogue.xlsx
+++ b/CodeSystem-pcor-score-catalogue.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T09:59:00+00:00</t>
+    <t>2026-10-01T11:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-pcor-score-catalogue.xlsx
+++ b/CodeSystem-pcor-score-catalogue.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:16:03+00:00</t>
+    <t>2026-10-01T11:25:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-pcor-score-catalogue.xlsx
+++ b/CodeSystem-pcor-score-catalogue.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:25:55+00:00</t>
+    <t>2026-10-01T11:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-pcor-score-catalogue.xlsx
+++ b/CodeSystem-pcor-score-catalogue.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T11:30:23+00:00</t>
+    <t>2026-10-01T13:09:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-pcor-score-catalogue.xlsx
+++ b/CodeSystem-pcor-score-catalogue.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:09:50+00:00</t>
+    <t>2026-10-01T14:39:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-pcor-score-catalogue.xlsx
+++ b/CodeSystem-pcor-score-catalogue.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T14:39:45+00:00</t>
+    <t>2026-10-01T14:59:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-pcor-score-catalogue.xlsx
+++ b/CodeSystem-pcor-score-catalogue.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T14:59:54+00:00</t>
+    <t>2026-10-13T13:38:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-pcor-score-catalogue.xlsx
+++ b/CodeSystem-pcor-score-catalogue.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T13:38:01+00:00</t>
+    <t>2026-10-13T14:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-pcor-score-catalogue.xlsx
+++ b/CodeSystem-pcor-score-catalogue.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T14:06:39+00:00</t>
+    <t>2026-10-14T13:27:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
